--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="292">
   <si>
     <t>S.No.</t>
   </si>
@@ -70,7 +70,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>Logged in as school-admin &lt;REPORTS_ADMIN_USER&gt;; school "Cqa Test Ashish School 1 (key VED-NEH-KVU)" opened from "My school accounts"; Reports tab open.</t>
+    <t>Logged in as school-admin &lt;REPORTS_ADMIN_USER&gt;; school "3 July Test School 1 (key FCN-CHZ-PDA)" opened from "My school accounts"; Reports tab open.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Open the school from "My school accounts".
@@ -84,7 +84,7 @@
     <t>URL is /admin/admin/org_&lt;slug&gt;/reports. The heading reads "Reports (0)". A "Create report" button is present. The informational line reads "Reports are available to download for up to 60 days". The empty state reads "No new reports available" above "Your reports will appear here after you create them", with a second "Create report" button.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. All copy captured verbatim live 2026-08-26. The (0) count is school-specific — on a school that already holds reports this case cannot show the empty state.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. All copy captured verbatim live 2026-08-26. The (0) count is school-specific — on a school that already holds reports this case cannot show the empty state.</t>
   </si>
   <si>
     <t/>
@@ -121,7 +121,7 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>Logged in as school-admin &lt;REPORTS_ADMIN_USER&gt;; school "Cqa Test Ashish School 1 (key VED-NEH-KVU)" opened; "Create report" clicked so the class-selection step is displayed.</t>
+    <t>Logged in as school-admin &lt;REPORTS_ADMIN_USER&gt;; school "3 July Test School 1 (key FCN-CHZ-PDA)" opened; "Create report" clicked so the class-selection step is displayed.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click the "Go back" link at the top of the class-selection step.
@@ -131,7 +131,7 @@
     <t>The app returns to /admin/admin/org_&lt;slug&gt;/reports, the Reports tab renders, and no new report has been created (the heading count is unchanged).</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Distinct from the footer "Cancel" (TST_MRPT_TC_18) — both exit paths need covering.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Distinct from the footer "Cancel" (TST_MRPT_TC_18) — both exit paths need covering.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_4</t>
@@ -143,18 +143,18 @@
     <t>#2 — Verify search using class name or class key</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Type "Gated LP Class" into the "Search for class name or class key" box.
-2. Click "Search".
+    <t xml:space="preserve">1. Type "Fixture_GradeSettings_DO_NOT_DELETE" into the "Search for class name or class key" box.
+2. Do NOT click "Search".
 3. Observe the class list.</t>
   </si>
   <si>
-    <t>Search term: Gated LP Class</t>
-  </si>
-  <si>
-    <t>The list narrows to the class "Gated LP Class" with key 4mG6-9Jkf, and the row remains selectable.</t>
-  </si>
-  <si>
-    <t>The search control is a text box plus an explicit "Search" button (captured live 2026-08-26). [ASSUMED] that, as on the Classes tab, typing alone does not filter and the button click is required.</t>
+    <t>Search term: Fixture_GradeSettings_DO_NOT_DELETE</t>
+  </si>
+  <si>
+    <t>The list narrows to the single class "Fixture_GradeSettings_DO_NOT_DELETE" with key 62k3-AXm6, WITHOUT the "Search" button being clicked, and the row remains selectable.</t>
+  </si>
+  <si>
+    <t>CORRECTED 2026-09-08 — the previous expected result was [ASSUMED] and WRONG. The search is LIVE / debounced, not submit-driven: the list narrowed to one row before the "Search" button was clicked. The earlier assumption was inherited from the Classes tab, which IS submit-driven — exactly the trap admin-shared.md §A4 warns about. A "Search" control (a[qid="createReport-10"]) does exist but is not required to filter. Test data also changed: the original "Gated LP Class" (4mG6-9Jkf) lives on VED-NEH-KVU, which the suite account cannot see. Fixture_GradeSettings_DO_NOT_DELETE is documented never-delete in admin-shared.md §A7, so it is unique and stable on this shared school.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_5</t>
@@ -163,18 +163,18 @@
     <t>Verify a class is returned when its class key is searched</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Type "4mG6-9Jkf" into the search box.
-2. Click "Search".
+    <t xml:space="preserve">1. Type "62k3-AXm6" into the search box.
+2. Do NOT click "Search".
 3. Observe the class list.</t>
   </si>
   <si>
-    <t>Search term: 4mG6-9Jkf</t>
-  </si>
-  <si>
-    <t>The list narrows to the single class whose Class key column reads "4mG6-9Jkf" ("Gated LP Class").</t>
-  </si>
-  <si>
-    <t>The placeholder offers both paths — "Search for class name or class key" — so the key path is covered separately from the name path.</t>
+    <t>Search term: 62k3-AXm6</t>
+  </si>
+  <si>
+    <t>The list narrows to the single class whose Class key column reads "62k3-AXm6" ("Fixture_GradeSettings_DO_NOT_DELETE").</t>
+  </si>
+  <si>
+    <t>Verified live 2026-09-08. The placeholder offers both paths — "Search for class name or class key" — so the key path is covered separately from the name path. Key changed from 4mG6-9Jkf (VED-NEH-KVU) to 62k3-AXm6 (FCN-CHZ-PDA) with the re-grounding. As with TC_4 the search is live — no "Search" click is required.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_6</t>
@@ -233,10 +233,10 @@
 2. Observe the panel.</t>
   </si>
   <si>
-    <t>A panel headed "Filter by" opens containing exactly five unticked checkboxes labelled "Not started", "Active", "Ended", "Expired" and "Deleted", plus a "Clear all" link, an "Apply" button and a "Close" control.</t>
-  </si>
-  <si>
-    <t>All strings captured verbatim live 2026-08-26. Note the status set includes "Not started", which the existing Classes-tab knowledge did not record (it listed Ended / Expired / Deleted).</t>
+    <t>A panel headed "Filter by" opens containing exactly five checkboxes labelled "Not started", "Active", "Ended", "Expired" and "Deleted", ALL FIVE TICKED by default, plus a "Clear all" link, an "Apply" button and a "Close" control. The filter summary label reads "All class statuses".</t>
+  </si>
+  <si>
+    <t>CORRECTED 2026-09-08 — the previous expected result said the five checkboxes were UNTICKED. They are all TICKED by default, which is what makes the unfiltered summary read "All class statuses". Strings otherwise captured verbatim live 2026-08-26 and re-verified 2026-09-08. Note the status set includes "Not started", which the existing Classes-tab knowledge did not record (it listed Ended / Expired / Deleted).</t>
   </si>
   <si>
     <t>TST_MRPT_TC_9</t>
@@ -246,39 +246,39 @@
   </si>
   <si>
     <t xml:space="preserve">1. Click "Filter".
-2. Tick "Active".
+2. Untick "Not started", "Ended", "Expired" and "Deleted", leaving only "Active" ticked.
 3. Click "Apply".
 4. Observe the class list and the filter summary label.</t>
   </si>
   <si>
-    <t>Filter: Active</t>
-  </si>
-  <si>
-    <t>The panel closes and every rendered row shows "Active" in its Class status column. The summary label that read "All class statuses" now reflects the applied filter instead.</t>
-  </si>
-  <si>
-    <t>[ASSUMED] for the exact summary-label text after applying — only the unfiltered "All class statuses" value was captured live. All six classes on VED-NEH-KVU were Active on 2026-08-26, so this school cannot prove exclusion; use a status with both a matching and a non-matching set.</t>
+    <t>Filter: Active only</t>
+  </si>
+  <si>
+    <t>The panel closes and every rendered row shows "Active" in its Class status column. The summary label changes from "All class statuses" to "1 class status".</t>
+  </si>
+  <si>
+    <t>VERIFIED live 2026-09-08 on FCN-CHZ-PDA; the [ASSUMED] on the summary label is resolved. The label is "&lt;N&gt; class status(es)" where N is the number of TICKED statuses — so leaving one ticked reads "1 class status" (singular). Steps corrected: because all five start ticked (TC_8), a single-status filter is reached by UNTICKING the other four, not by ticking one. This school proves exclusion properly — 21 of its 110 classes are Active, and the pre-filter list contained Deleted rows.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_10</t>
   </si>
   <si>
-    <t>Verify all status selections are cleared when "Clear all" is used</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click "Filter".
-2. Tick "Active" and "Ended".
+    <t>Verify the unfiltered class list is restored when "Clear all" is used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Apply a filter of a single status (see TST_MRPT_TC_9) so the summary reads "1 class status".
+2. Click "Filter" to reopen the panel.
 3. Click "Clear all".
-4. Observe the checkboxes and the class list.</t>
-  </si>
-  <si>
-    <t>Filter: Active + Ended, then Clear all</t>
-  </si>
-  <si>
-    <t>All five status checkboxes return to unticked. [ASSUMED] the class list returns to the unfiltered set and the summary label returns to "All class statuses".</t>
-  </si>
-  <si>
-    <t>[ASSUMED] — whether "Clear all" applies immediately or still requires a subsequent "Apply" was NOT determined live. This is the most likely place in this group for a wrong expected result; resolve it first.</t>
+4. Observe the checkboxes, the panel, the class list and the summary label.</t>
+  </si>
+  <si>
+    <t>A single applied status, then Clear all</t>
+  </si>
+  <si>
+    <t>All five status checkboxes return to TICKED, the panel closes immediately WITHOUT "Apply" being clicked, the class list returns to the unfiltered set and the summary label returns to "All class statuses".</t>
+  </si>
+  <si>
+    <t>CORRECTED 2026-09-08 — both [ASSUMED]s resolved, and the previous expected result was WRONG. "Clear all" is a RESET TO UNFILTERED, not an "untick everything": it re-checks all five statuses, applies immediately with no "Apply" click, and closes the panel. This was flagged in the original Remarks as the most likely place for a wrong expected result, and it was.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_11</t>
@@ -335,36 +335,38 @@
     <t>#4 — Verify class selection checkbox</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Tick the "Select class" checkbox on the "Gated LP Class" row.
-2. Observe the section heading and the bottom of the page.</t>
-  </si>
-  <si>
-    <t>Class: "Gated LP Class" (4mG6-9Jkf), 1 student</t>
-  </si>
-  <si>
-    <t>The section heading becomes "Select classes(1)". A footer bar appears reading "You have selected 1 class with a total of 1 student" and carrying a "Cancel" link and a "Continue" button.</t>
-  </si>
-  <si>
-    <t>Captured live 2026-08-26. Both the "(1)" suffix and the whole footer bar are absent at zero selection — see TST_MRPT_TC_15.</t>
+    <t xml:space="preserve">1. Search for "Fixture_GradeSettings_DO_NOT_DELETE" so the list holds a single known row.
+2. Tick that row's "Select class" checkbox.
+3. Observe the section heading and the bottom of the page.</t>
+  </si>
+  <si>
+    <t>Class: "Fixture_GradeSettings_DO_NOT_DELETE" (62k3-AXm6), 0 students</t>
+  </si>
+  <si>
+    <t>The section heading becomes "Select classes(1)". A footer bar appears reading "You have selected 1 class with a total of 0 students" and carrying a "Cancel" link and a "Continue" button.</t>
+  </si>
+  <si>
+    <t>Re-verified live 2026-09-08 on FCN-CHZ-PDA. Both the "(1)" suffix and the whole footer bar are absent at zero selection — see TST_MRPT_TC_15. NOTE the summary says "0 studentS" — plural with a zero count; the singular "1 student" form recorded on 2026-08-26 came from a different class. Do not assert a singular/plural rule. The footer appears on the SAME TICK as the click (measured 0 ms).</t>
   </si>
   <si>
     <t>TST_MRPT_TC_14</t>
   </si>
   <si>
-    <t>Verify every listed class is selected when "Select all classes" is ticked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tick the "Select all classes" checkbox.
-2. Observe the row checkboxes, the section heading and the footer bar.</t>
-  </si>
-  <si>
-    <t>6 classes on VED-NEH-KVU, 1 student each</t>
-  </si>
-  <si>
-    <t>Every class row checkbox becomes ticked, the heading reads "Select classes(&lt;N&gt;)" where &lt;N&gt; is the number of listed classes, and the footer bar summarises the same totals (e.g. "You have selected 6 classes with a total of 6 students").</t>
-  </si>
-  <si>
-    <t>[ASSUMED] plural wording ("classes" / "students") — only the singular "1 class" / "1 student" form was captured live. Also confirm whether "Select all" covers only the currently searched/filtered rows or every class on the school.</t>
+    <t>Verify every matching class is selected when "Select all classes" is ticked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. With no search or filter applied, note how many class rows are rendered (the list lazy-loads 20 at a time and offers "Load more...").
+2. Tick the "Select all classes" checkbox.
+3. Observe the row checkboxes, the section heading and the footer bar.</t>
+  </si>
+  <si>
+    <t>FCN-CHZ-PDA: 110 classes in total, 20 rendered per page, 30 students across the school</t>
+  </si>
+  <si>
+    <t>Every RENDERED row checkbox becomes ticked. The heading reads "Select classes(&lt;TOTAL&gt;)" where &lt;TOTAL&gt; is the number of classes MATCHING the current query — the full 110, not the 20 rendered — and the footer bar summarises the same totals ("You have selected 110 classes with a total of 30 students").</t>
+  </si>
+  <si>
+    <t>RESOLVED live 2026-09-08 — the open question in the original Remarks is answered: "Select all" covers EVERY MATCHING class on the school, not just the loaded page. With 20 of 110 rows rendered the heading read "Select classes(110)". So an expected result of the form "&lt;N&gt; = the number of listed classes" is WRONG and would fail. Plural wording confirmed ("classes" / "students"). When automating, do not hardcode 110 — this school churns; assert the heading count against the createReport-11-N anchor count, which tracks the matching total. Also: clicking select-all while a PARTIAL selection exists clears it instead of completing it, so reaching "all selected" from one ticked row takes two clicks.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_15</t>
@@ -422,7 +424,7 @@
     <t>[ASSUMED] Selection is capped at 1500 and the product surfaces the limit it states on screen ("You can include up to 1500 classes").</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. The cap text is captured verbatim live, but VED-NEH-KVU holds only 6 classes so the cap cannot be reached. UNBLOCK: a dedicated school seeded with &gt;1500 classes, or a product/API confirmation. Whether the cap blocks further ticks or raises a message is unknown.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. The cap text is captured verbatim live, but VED-NEH-KVU holds only 6 classes so the cap cannot be reached. UNBLOCK: a dedicated school seeded with &gt;1500 classes, or a product/API confirmation. Whether the cap blocks further ticks or raises a message is unknown.</t>
   </si>
   <si>
     <t>Blocked</t>
@@ -434,7 +436,7 @@
     <t>TST_MRPT_TC_18</t>
   </si>
   <si>
-    <t>Verify the Reports tab is restored and no report is created when "Cancel" is used on the class-selection step</t>
+    <t>Verify the class selection is cleared and no report is created when "Cancel" is used on the class-selection step</t>
   </si>
   <si>
     <t>#5 — Verify Cancel button functionality</t>
@@ -442,16 +444,16 @@
   <si>
     <t xml:space="preserve">1. Tick one class checkbox so the footer bar appears.
 2. Click "Cancel" in the footer bar.
-3. Observe the page and the Reports list.</t>
-  </si>
-  <si>
-    <t>Class: "Gated LP Class" (4mG6-9Jkf)</t>
-  </si>
-  <si>
-    <t>The app returns to /admin/admin/org_&lt;slug&gt;/reports and the Reports heading count is unchanged — no report has been created.</t>
-  </si>
-  <si>
-    <t>This is the step-1 Cancel. A SECOND, separate Cancel exists inside the "Create report" dialog (TST_MRPT_TC_19) — the two must not be conflated.</t>
+3. Observe the row checkbox, the section heading, the footer bar and the URL.</t>
+  </si>
+  <si>
+    <t>Class: "Fixture_GradeSettings_DO_NOT_DELETE" (62k3-AXm6)</t>
+  </si>
+  <si>
+    <t>The class is deselected, the section heading returns to a bare "Select classes" with no "(N)" suffix and the footer bar is removed from the page. The app REMAINS on /admin/admin/org_&lt;slug&gt;/reports/create. No report is created.</t>
+  </si>
+  <si>
+    <t>CORRECTED 2026-09-08 — the previous expected result ("the app returns to the Reports tab") was WRONG and had never been verified live. Reproduced twice, the second time on a freshly reloaded page, with no dialog, no backdrop and 0 visible modals: the footer "Cancel" (createReport-13) CLEARS THE SELECTION and stays on the class-selection step. The control that leaves the flow is "Go back" (createReport-1), covered by TST_MRPT_TC_3, which was verified returning to /reports with "Reports (0)" unchanged. Confirmed as accepted product behaviour by the user 2026-09-08 — NOT raised as a defect. There are now THREE distinct Cancel-like controls on this flow: createReport-1 leaves, createReport-13 clears the selection, createReport-15 closes the config dialog (TST_MRPT_TC_19). They must not be conflated.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_19</t>
@@ -462,18 +464,18 @@
   <si>
     <t xml:space="preserve">1. Tick one class checkbox.
 2. Click "Continue" to open the "Create report" dialog.
-3. Choose a report type.
+3. Choose report type "Class summary".
 4. Click "Cancel" in the dialog.
-5. Observe the page and the Reports list.</t>
-  </si>
-  <si>
-    <t>Class: "Gated LP Class" · Report type: "Class summary"</t>
-  </si>
-  <si>
-    <t>[ASSUMED] The dialog closes and the class-selection step is shown again with the class still selected; no report is created.</t>
-  </si>
-  <si>
-    <t>[ASSUMED] — whether the dialog Cancel preserves the class selection, clears it, or returns all the way to the Reports tab was NOT verified live. Confirm before automating.</t>
+5. Observe the dialog, the class selection and the URL.</t>
+  </si>
+  <si>
+    <t>Class: "Fixture_GradeSettings_DO_NOT_DELETE" (62k3-AXm6) · Report type: "Class summary"</t>
+  </si>
+  <si>
+    <t>The dialog closes and the class-selection step is shown again with the class STILL SELECTED — heading still "Select classes(1)", footer bar still present. The report type resets to "Select a report type". The app remains on /admin/admin/org_&lt;slug&gt;/reports/create and no report is created.</t>
+  </si>
+  <si>
+    <t>VERIFIED live 2026-09-08 — the [ASSUMED] is resolved and the guess was right: the dialog Cancel PRESERVES the class selection. It does not clear it and does not return to the Reports tab. The dialog (#schoolReportModal) stays in the DOM at display:none, so assert visibility, never presence. The report type resetting to "Select a report type" is an additional confirmed detail. This case could not be confirmed on 2026-09-07 because the browser session was degraded, not because the product misbehaved.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_20</t>
@@ -719,7 +721,7 @@
     <t>Dates before 1 January 2022 are not selectable; 1 January 2022 itself is selectable.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26 from the field attributes: the "From" input carries min="2021-12-31T18:30:00.000Z", i.e. 2022-01-01 in IST. Exactly the kind of field constraint admin-shared.md §A3 requires be read before writing boundary cases.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26 from the field attributes: the "From" input carries min="2021-12-31T18:30:00.000Z", i.e. 2022-01-01 in IST. Exactly the kind of field constraint admin-shared.md §A3 requires be read before writing boundary cases.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_30</t>
@@ -739,7 +741,7 @@
     <t>All dates after today are disabled in both pickers; today is selectable in both.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26: both inputs carry max="2026-08-26T18:29:59.999Z" (end of the current day). Reports cover past activity only.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26: both inputs carry max="2026-08-26T18:29:59.999Z" (end of the current day). Reports cover past activity only.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_31</t>
@@ -780,7 +782,7 @@
     <t>Neither field accepts typed input; both retain their picker-set values. Dates can be set only through the calendar pickers.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26: both "From" and "To" inputs are readOnly. This rules out the whole family of "type an invalid date" negative cases — the pickers are the only input path.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26: both "From" and "To" inputs are readOnly. This rules out the whole family of "type an invalid date" negative cases — the pickers are the only input path.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_33</t>
@@ -801,7 +803,7 @@
     <t>For all three types the "Custom date range" radio remains DISABLED and "From the beginning" stays selected — no "From"/"To" fields can be produced.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26 across all seven types. Date range is supported by exactly four (Class summary, Class detailed data, Class daily data, Aggregated data), which matches the four named in scenario #12 — the scenario list is correct, and this case pins the negative half of it.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26 across all seven types. Date range is supported by exactly four (Class summary, Class detailed data, Class daily data, Aggregated data), which matches the four named in scenario #12 — the scenario list is correct, and this case pins the negative half of it.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_34</t>
@@ -834,7 +836,7 @@
     <t>Verify the created report is restricted to grade-contributing items when the custom grade option is ticked</t>
   </si>
   <si>
-    <t>Logged in as school-admin &lt;REPORTS_ADMIN_USER&gt;; school "Cqa Test Ashish School 1 (key VED-NEH-KVU)" opened; "Create report" clicked so the class-selection step is displayed. The chosen class has Class grade settings configured so that at least one component is excluded from grade calculation.</t>
+    <t>Logged in as school-admin &lt;REPORTS_ADMIN_USER&gt;; school "3 July Test School 1 (key FCN-CHZ-PDA)" opened; "Create report" clicked so the class-selection step is displayed. The chosen class has Class grade settings configured so that at least one component is excluded from grade calculation.</t>
   </si>
   <si>
     <t xml:space="preserve">1. Tick a class whose grade settings exclude a component, and click "Continue".
@@ -872,7 +874,7 @@
     <t>The checkbox is DISABLED and cannot be ticked.</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26. Estimated CEFR level is the only one of the seven types supporting neither a custom date range nor custom grade settings — which is why it appears in neither scenario #12 nor #13.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26. Estimated CEFR level is the only one of the seven types supporting neither a custom date range nor custom grade settings — which is why it appears in neither scenario #12 nor #13.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_37</t>
@@ -924,7 +926,7 @@
     <t>A dialog is shown headed "Sorry, something went wrong. The report you requested was not generated." offering "Try again" and "Back to Reports".</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. The copy above was captured verbatim from the PRE-RENDERED DOM on 2026-08-26 (admin-shared.md §A6 free-capture), so the expected result is verified even though the state was never reached. UNBLOCK: backend fault injection or a stubbed failure response. A second, separate failure surface exists on the Reports tab itself — see TST_MRPT_TC_39.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. The copy above was captured verbatim from the PRE-RENDERED DOM on 2026-08-26 (admin-shared.md §A6 free-capture), so the expected result is verified even though the state was never reached. UNBLOCK: backend fault injection or a stubbed failure response. A second, separate failure surface exists on the Reports tab itself — see TST_MRPT_TC_39.</t>
   </si>
   <si>
     <t>Blocked at design time — report generation failure cannot be forced on Thor.</t>
@@ -947,7 +949,7 @@
     <t>A modal headed "Report created with errors" states "&lt;N&gt; out of &lt;TOTAL&gt; classes were not included in your report due to the errors shown below" above a table with the columns "Class name", "Class key" and "Error message", and offers "Download report".</t>
   </si>
   <si>
-    <t>[EXTRA — Phase 1 exclusion] Not present in the other team's reviewed sheet (Admin_Gap_Analysis.xlsx, status "Extra in Ours"). This case will NOT be automated in Phase 1 — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. Copy captured from the pre-rendered DOM on the Reports tab 2026-08-26. Requires a multi-class report in which some classes fail — cannot be produced on demand. UNBLOCK: fault injection, or a class deliberately placed in a state that fails report generation.</t>
+    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. Copy captured from the pre-rendered DOM on the Reports tab 2026-08-26. Requires a multi-class report in which some classes fail — cannot be produced on demand. UNBLOCK: fault injection, or a class deliberately placed in a state that fails report generation.</t>
   </si>
   <si>
     <t>Blocked at design time — a partially-failing report cannot be produced on Thor.</t>
@@ -956,25 +958,19 @@
     <t>TST_MRPT_TC_40</t>
   </si>
   <si>
-    <t>Verify the report class-selection filter narrows the list by class label</t>
-  </si>
-  <si>
-    <t>#3 - Verify filter</t>
-  </si>
-  <si>
-    <t>In the report creation flow at the class-selection step, on a school with at least one labelled class.</t>
-  </si>
-  <si>
-    <t>1. Click Create report to reach class selection. 2. Open Filter. 3. Record which filter groups the panel offers. 4. If class labels are offered, select one and Apply. 5. Read the resulting class list.</t>
-  </si>
-  <si>
-    <t>Label &lt;EXISTING_THOR_CLASS_LABEL&gt;.</t>
-  </si>
-  <si>
-    <t>The class list is narrowed to classes carrying the selected label, and a label combined with a status behaves as an AND. [ASSUMED] - and the premise itself is unconfirmed.</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 from the other team's TC_REP_003, which says "status/label filter". All five of our filter cases (TST_MRPT_TC_8-TC_12) are class-STATUS only, and TST_MRPT_TC_8 asserts the panel opens with five class statuses - with no mention of labels. GROUND FIRST: if the report-flow panel offers statuses only, their sheet is wrong and this becomes a correction rather than a new case. The label filter definitely exists on the Classes tab (TST_CLST_TC_4); whether the report flow reuses that panel is the open question. Read-only.</t>
+    <t>Verify the class-selection filter offers class statuses only and no class-label filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click "Create report" to reach the class-selection step.
+2. Open "Filter".
+3. Record every filter group the panel offers.
+4. Confirm no class-label group is present.</t>
+  </si>
+  <si>
+    <t>The filter panel offers EXACTLY ONE group — the five class statuses ("Not started", "Active", "Ended", "Expired", "Deleted") — and no class-label filter of any kind. The panel contains exactly five checkboxes in total.</t>
+  </si>
+  <si>
+    <t>REWRITTEN 2026-09-08 by user decision. Originally added 2026-09-01 from the other team's TC_REP_003, which describes a "status/label filter", and the case asked whether the filter narrows the list by class LABEL. Its own Remarks flagged the premise as unconfirmed and said GROUND FIRST. Grounded live 2026-09-08: the premise is FALSE — the report-flow panel offers five status checkboxes and no other group, so the other team's sheet is wrong on this point. The case is therefore inverted into an expected-versus-actual assertion that PINS the absence of a label filter. A class-label filter does exist on the Classes tab (TST_CLST_TC_4); the report flow does not reuse that panel. Read-only.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_41</t>
@@ -983,13 +979,13 @@
     <t>Verify a generated report contains data that reconciles with the class it was run against</t>
   </si>
   <si>
-    <t>#6 - Verify Class summary report from beginning</t>
-  </si>
-  <si>
     <t>A fixture class whose activity data is known and stable, with a report generated over it.</t>
   </si>
   <si>
-    <t>1. Record the fixture class's known activity - enrolled students and their completed activities/scores. 2. Generate a Class summary report "From the beginning" and download it. 3. Reconcile the file against the recorded data: one row per enrolled student, totals summing correctly. 4. Repeat for Aggregated data and confirm its figures sum/average the underlying class-level data.</t>
+    <t xml:space="preserve">1. Record the fixture class's known activity — enrolled students and their completed activities/scores.
+2. Generate a "Class summary" report "From the beginning" and download it.
+3. Reconcile the file against the recorded data: one row per enrolled student, totals summing correctly.
+4. Repeat for "Aggregated data" and confirm its figures sum/average the underlying class-level data.</t>
   </si>
   <si>
     <t>Fixture class &lt;FROZEN_ACTIVITY_CLASS&gt; with known, unchanging activity.</t>
@@ -998,10 +994,10 @@
     <t>The downloaded report reflects the class's actual data: every enrolled student is represented, totals and averages are arithmetically correct, and no activity outside the requested window appears. [ASSUMED]</t>
   </si>
   <si>
-    <t>Added 2026-09-01 - the most significant gap found in the whole comparison. Our seven generation cases (TST_MRPT_TC_21-TC_26, TC_37) all stop at "the report is created and listed for download"; every one of the other team's equivalents (TC_REP_006-TC_REP_012) asserts the numbers inside. A report that generates successfully with wrong content passes every case we currently hold. Written against Class summary and Aggregated data as the two highest-value types; extend to the rest once the fixture exists.</t>
-  </si>
-  <si>
-    <t>Blocked at design time (skill rule 4): reconciliation needs a class whose activity is seeded and frozen. 3 July Test School 1 is shared and its activity changes under other suites, so figures would not be reproducible. Unblock by provisioning a fixture class with known, stable activity data - this is the single most valuable fixture on the Reports backlog.</t>
+    <t>Added 2026-09-01 — the most significant gap found in the whole comparison. Our seven generation cases (TST_MRPT_TC_21–TC_26, TC_37) all stop at "the report is created and listed for download"; every one of the other team's equivalents (TC_REP_006–TC_REP_012) asserts the numbers inside. A report that generates successfully with WRONG CONTENT passes every case we currently hold. Written against Class summary and Aggregated data as the two highest-value types; extend to the rest once the fixture exists.</t>
+  </si>
+  <si>
+    <t>Blocked at design time (skill rule 4): reconciliation needs a class whose activity is seeded and frozen. "3 July Test School 1" is shared and its activity changes under other suites, so figures would not be reproducible. Unblock by provisioning a fixture class with known, stable activity data — this is the single most valuable fixture on the Reports backlog.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_42</t>
@@ -1010,13 +1006,12 @@
     <t>Verify a custom grade exclusion is respected consistently across every report type that supports it</t>
   </si>
   <si>
-    <t>#13 - Verify reports with custom grade settings applied</t>
-  </si>
-  <si>
     <t>A class whose grade settings exclude one component or category from the grade, with known activity on the excluded item.</t>
   </si>
   <si>
-    <t>1. Configure the class grade settings to exclude one component/category. 2. Generate each supported type with the custom grade option ticked: Class summary, Class detailed data, Class daily data, Aggregated data, Assignments summary, Assignments detailed data. 3. In each output, confirm the excluded item is absent and the totals recompute without it.</t>
+    <t xml:space="preserve">1. Configure the class grade settings to exclude one component/category.
+2. Generate each supported type with the custom grade option ticked: Class summary, Class detailed data, Class daily data, Aggregated data, Assignments summary, Assignments detailed data.
+3. In each output, confirm the excluded item is absent and the totals recompute without it.</t>
   </si>
   <si>
     <t>Class &lt;FROZEN_ACTIVITY_CLASS&gt; with one component excluded from the grade.</t>
@@ -1025,7 +1020,7 @@
     <t>All six report types consistently omit the excluded component and recompute their totals/averages without it. [ASSUMED]</t>
   </si>
   <si>
-    <t>Added 2026-09-01 from the other team's TC_REP_014, which sweeps the exclusion across all six types. Our TST_MRPT_TC_35 proves the option takes effect on one report; consistency across types was untested - and inconsistency between report types is precisely the defect this guards against. Depends on the same fixture as TST_MRPT_TC_41.</t>
+    <t>Added 2026-09-01 from the other team's TC_REP_014, which sweeps the exclusion across all six types. Our TST_MRPT_TC_35 proves the option takes effect on ONE report; consistency across types was untested — and inconsistency between report types is precisely the defect this guards against. Depends on the same fixture as TST_MRPT_TC_41.</t>
   </si>
   <si>
     <t>Blocked at design time: depends on the seeded, frozen-activity fixture class described in TST_MRPT_TC_41. Unblock together.</t>
@@ -3209,7 +3204,7 @@
         <v>272</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>273</v>
+        <v>67</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>17</v>
@@ -3218,19 +3213,19 @@
         <v>34</v>
       </c>
       <c r="G41" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="H41" s="2" t="s">
+      <c r="K41" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>24</v>
@@ -3247,13 +3242,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>281</v>
+        <v>150</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>17</v>
@@ -3262,19 +3257,19 @@
         <v>18</v>
       </c>
       <c r="G42" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="K42" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>24</v>
@@ -3283,7 +3278,7 @@
         <v>127</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3291,13 +3286,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>290</v>
+        <v>231</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>33</v>
@@ -3306,19 +3301,19 @@
         <v>34</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>24</v>
@@ -3327,11 +3322,11 @@
         <v>127</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="293">
   <si>
     <t>S.No.</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>Captured live 2026-08-26. Note the "Select classes" heading carries NO count while zero classes are selected — the "(N)" appears only once at least one class is ticked.</t>
+  </si>
+  <si>
+    <t>Pass</t>
   </si>
   <si>
     <t>TST_MRPT_TC_3</t>
@@ -1559,7 +1562,7 @@
         <v>24</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>24</v>
@@ -1570,34 +1573,34 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>24</v>
@@ -1614,13 +1617,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>17</v>
@@ -1629,25 +1632,25 @@
         <v>18</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>24</v>
@@ -1658,13 +1661,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>17</v>
@@ -1673,25 +1676,25 @@
         <v>18</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>24</v>
@@ -1702,34 +1705,34 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>24</v>
@@ -1746,34 +1749,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>24</v>
@@ -1790,40 +1793,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>24</v>
@@ -1834,13 +1837,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>17</v>
@@ -1849,25 +1852,25 @@
         <v>18</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>24</v>
@@ -1878,34 +1881,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>24</v>
@@ -1922,34 +1925,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>24</v>
@@ -1966,34 +1969,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>24</v>
@@ -2010,13 +2013,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>17</v>
@@ -2025,25 +2028,25 @@
         <v>18</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>24</v>
@@ -2054,13 +2057,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>17</v>
@@ -2069,25 +2072,25 @@
         <v>18</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>24</v>
@@ -2098,34 +2101,34 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>24</v>
@@ -2142,34 +2145,34 @@
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>24</v>
@@ -2186,43 +2189,43 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2230,13 +2233,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>17</v>
@@ -2245,25 +2248,25 @@
         <v>18</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>24</v>
@@ -2274,40 +2277,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>24</v>
@@ -2318,34 +2321,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>24</v>
@@ -2362,13 +2365,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>17</v>
@@ -2377,25 +2380,25 @@
         <v>18</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>24</v>
@@ -2406,13 +2409,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>17</v>
@@ -2421,25 +2424,25 @@
         <v>18</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>24</v>
@@ -2450,13 +2453,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>17</v>
@@ -2465,25 +2468,25 @@
         <v>18</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>24</v>
@@ -2494,13 +2497,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>17</v>
@@ -2509,25 +2512,25 @@
         <v>18</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>24</v>
@@ -2538,40 +2541,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>24</v>
@@ -2582,40 +2585,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>24</v>
@@ -2626,13 +2629,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>17</v>
@@ -2641,25 +2644,25 @@
         <v>18</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>24</v>
@@ -2670,13 +2673,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>17</v>
@@ -2685,25 +2688,25 @@
         <v>18</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>24</v>
@@ -2714,34 +2717,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>24</v>
@@ -2758,34 +2761,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>24</v>
@@ -2802,34 +2805,34 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>24</v>
@@ -2846,34 +2849,34 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>24</v>
@@ -2890,34 +2893,34 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>24</v>
@@ -2934,13 +2937,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>17</v>
@@ -2949,25 +2952,25 @@
         <v>18</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>24</v>
@@ -2978,13 +2981,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>17</v>
@@ -2993,19 +2996,19 @@
         <v>18</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>24</v>
@@ -3022,34 +3025,34 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>24</v>
@@ -3066,13 +3069,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>17</v>
@@ -3081,25 +3084,25 @@
         <v>18</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>24</v>
@@ -3110,43 +3113,43 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3154,43 +3157,43 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3198,40 +3201,40 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>24</v>
@@ -3242,13 +3245,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>17</v>
@@ -3257,28 +3260,28 @@
         <v>18</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3286,43 +3289,43 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
   </sheetData>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
@@ -1738,7 +1738,7 @@
         <v>24</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>24</v>
@@ -1782,7 +1782,7 @@
         <v>24</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>24</v>
@@ -1914,7 +1914,7 @@
         <v>24</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>24</v>
@@ -1958,7 +1958,7 @@
         <v>24</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>24</v>
@@ -2002,7 +2002,7 @@
         <v>24</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>24</v>
@@ -2134,7 +2134,7 @@
         <v>24</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>24</v>
@@ -2178,7 +2178,7 @@
         <v>24</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>24</v>
@@ -2354,7 +2354,7 @@
         <v>24</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>24</v>
@@ -2838,7 +2838,7 @@
         <v>24</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>24</v>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="299">
   <si>
     <t>S.No.</t>
   </si>
@@ -1027,6 +1027,27 @@
   </si>
   <si>
     <t>Blocked at design time: depends on the seeded, frozen-activity fixture class described in TST_MRPT_TC_41. Unblock together.</t>
+  </si>
+  <si>
+    <t>TST_MRPT_TC_43</t>
+  </si>
+  <si>
+    <t>Verify the downloaded report file is well formed and contains the right class and students</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Create a "Class summary" report over the fixture class and return to the Reports tab.
+2. Wait for the new row to offer "Download", then click it.
+3. Unzip the downloaded archive.
+4. Open each CSV inside it and check the header row and the data rows.</t>
+  </si>
+  <si>
+    <t>Class: "Automation_class_DND" (z698-JPfC), 2 students: cqa_stu8sept@mailsac.com, cqa_student12jan@mailsac.com</t>
+  </si>
+  <si>
+    <t>The download is a ZIP containing at least one CSV, one per product component, named "&lt;product&gt; &lt;component&gt;_&lt;DD-MMM-YYYY&gt;_&lt;report type&gt; report.csv". Every CSV has 19 columns beginning with the fixed identity block "First name, Last name, Email, Username, Class name, Class key, Product, Component". Every data row carries Class name "Automation_class_DND" and Class key "z698-JPfC". Each CSV holds exactly one row per enrolled student (2), and the set of Email values equals the class roster.</t>
+  </si>
+  <si>
+    <t>ADDED 2026-09-11 after a real report was downloaded and inspected — the first case in this register to look INSIDE the file. Until now every generation case (TST_MRPT_TC_21–TC_26, TC_28, TC_37) stopped at "a row appeared in the list", so a report generated with entirely wrong CONTENT passed all of them. This case closes the structural half of that gap: empty file, corrupt ZIP, wrong class, a missing student, or changed columns are all now caught. It does NOT reconcile the activity NUMBERS (scores, completion, time spent) — that still needs the frozen-activity fixture and remains TST_MRPT_TC_41, which stays Blocked. TWO THINGS ARE DELIBERATELY NOT ASSERTED: (1) the exact label of column 14, which varies by component — observed as "Best attempts above target score (Gold Medals)" on two CSVs and "Best attempts above target score" on the third; (2) the NUMBER of CSVs, which follows the product's component count and would fail on a product change rather than a defect. Runs in the data-owning suite because a report must exist before it can be downloaded.</t>
   </si>
 </sst>
 </file>
@@ -1418,7 +1439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -3328,6 +3349,50 @@
         <v>292</v>
       </c>
     </row>
+    <row r="44" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="298">
   <si>
     <t>S.No.</t>
   </si>
@@ -982,25 +982,23 @@
     <t>Verify a generated report contains data that reconciles with the class it was run against</t>
   </si>
   <si>
-    <t>A fixture class whose activity data is known and stable, with a report generated over it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Record the fixture class's known activity — enrolled students and their completed activities/scores.
-2. Generate a "Class summary" report "From the beginning" and download it.
-3. Reconcile the file against the recorded data: one row per enrolled student, totals summing correctly.
-4. Repeat for "Aggregated data" and confirm its figures sum/average the underlying class-level data.</t>
-  </si>
-  <si>
-    <t>Fixture class &lt;FROZEN_ACTIVITY_CLASS&gt; with known, unchanging activity.</t>
-  </si>
-  <si>
-    <t>The downloaded report reflects the class's actual data: every enrolled student is represented, totals and averages are arithmetically correct, and no activity outside the requested window appears. [ASSUMED]</t>
-  </si>
-  <si>
-    <t>Added 2026-09-01 — the most significant gap found in the whole comparison. Our seven generation cases (TST_MRPT_TC_21–TC_26, TC_37) all stop at "the report is created and listed for download"; every one of the other team's equivalents (TC_REP_006–TC_REP_012) asserts the numbers inside. A report that generates successfully with WRONG CONTENT passes every case we currently hold. Written against Class summary and Aggregated data as the two highest-value types; extend to the rest once the fixture exists.</t>
-  </si>
-  <si>
-    <t>Blocked at design time (skill rule 4): reconciliation needs a class whose activity is seeded and frozen. "3 July Test School 1" is shared and its activity changes under other suites, so figures would not be reproducible. Unblock by provisioning a fixture class with known, stable activity data — this is the single most valuable fixture on the Reports backlog.</t>
+    <t>Logged in as the Reports school-admin; the FROZEN fixture class "Automation_frozen_DND" (gHoZ-iBXf) exists on VED-NEH-KVU with 2 enrolled students whose activity is known and unchanging.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Create a "Class summary" report over "Automation_frozen_DND" and return to the Reports tab.
+2. Wait for the new row to offer "Download", then download and unzip it.
+3. Locate each component's CSV by its Component COLUMN (not by filename or position).
+4. For the component that holds the activity ("Project Work"), reconcile every student row against the known activity.
+5. Confirm the components with no activity report none.</t>
+  </si>
+  <si>
+    <t>Class "Automation_frozen_DND" (gHoZ-iBXf). cqatestauto_stu1@mailsac.com performed 3 activities; cqatestauto_stu2@mailsac.com performed 1. Product total: 24 activities on the "Project Work" component.</t>
+  </si>
+  <si>
+    <t>The "Project Work" CSV holds one row per enrolled student, each carrying Class name "Automation_frozen_DND" and Class key "gHoZ-iBXf". cqatestauto_stu1 reports 3 activities completed of 24 (13%), best and first score average 72. cqatestauto_stu2 reports 1 of 24 (4%), best and first score average 67. The percentage is arithmetically consistent with completed/total in every row. Both students show a non-zero Time spent and a Last active value. The CSVs for "Practice Extra" and "Practice Extra - Group Enabled" report no completed activities and 00:00:00 time spent for either student.</t>
+  </si>
+  <si>
+    <t>UNBLOCKED AND AUTOMATED 2026-09-11 — the fixture was provisioned by the user specifically for this. THE POINT OF THIS CASE, and why it is worth the fixture: our eight generation cases (TST_MRPT_TC_21–TC_26, TC_28, TC_37) all stop at "a row appeared in the list", and TST_MRPT_TC_43 checks the file's structure and identity — a report generated with the WRONG NUMBERS passes all nine. This is the only case that reads the figures. The completed counts (3 and 1) are the one expectation here that did NOT come from the product: the user performed that activity and stated the counts BEFORE the report was read, and the report then agreed. That makes this a genuine correctness check; the score averages and totals are frozen snapshots and only catch regressions. The percentage is additionally asserted against its own arithmetic (round(completed/total*100)), which needs no frozen value and keeps working if the fixture is ever re-baselined. DELIBERATELY NOT ASSERTED AS VALUES: "Time spent" (00:02:40 / 00:00:50) and "Last active" (11-Sep-2026-11:10:18am / 11:13:12am) — both move the moment anyone opens the content, so only their presence or absence is checked. 🚨 NEVER MODIFY "Automation_frozen_DND": no enrolment changes, no material or grade-settings changes, and never log in as cqatestauto_stu1/stu2 and touch content. The day someone does, this case fails and it is NOT a product defect.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_42</t>
@@ -1026,7 +1024,7 @@
     <t>Added 2026-09-01 from the other team's TC_REP_014, which sweeps the exclusion across all six types. Our TST_MRPT_TC_35 proves the option takes effect on ONE report; consistency across types was untested — and inconsistency between report types is precisely the defect this guards against. Depends on the same fixture as TST_MRPT_TC_41.</t>
   </si>
   <si>
-    <t>Blocked at design time: depends on the seeded, frozen-activity fixture class described in TST_MRPT_TC_41. Unblock together.</t>
+    <t>Blocked at design time. The frozen-activity fixture it needed NOW EXISTS (Automation_frozen_DND / gHoZ-iBXf, provisioned 2026-09-11 and used by TST_MRPT_TC_41), so the remaining blocker is narrower than it was: that class still needs ONE COMPONENT EXCLUDED from its grade settings, and activity on the excluded item. Once that is configured this case can follow TST_MRPT_TC_41 directly.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_43</t>
@@ -3299,10 +3297,10 @@
         <v>24</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>284</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3310,10 +3308,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>232</v>
@@ -3325,19 +3323,19 @@
         <v>35</v>
       </c>
       <c r="G43" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="I43" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="I43" s="2" t="s">
+      <c r="J43" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="J43" s="2" t="s">
+      <c r="K43" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>24</v>
@@ -3346,7 +3344,7 @@
         <v>128</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3354,10 +3352,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>151</v>
@@ -3372,16 +3370,16 @@
         <v>36</v>
       </c>
       <c r="H44" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="I44" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="I44" s="2" t="s">
+      <c r="J44" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="J44" s="2" t="s">
+      <c r="K44" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>24</v>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="310">
   <si>
     <t>S.No.</t>
   </si>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t>Comments / Defect ID</t>
+  </si>
+  <si>
+    <t>Automation Status</t>
+  </si>
+  <si>
+    <t>Automation Evidence</t>
   </si>
   <si>
     <t>TST_MRPT_TC_1</t>
@@ -93,6 +99,12 @@
     <t>Not Run</t>
   </si>
   <si>
+    <t>Excluded - Phase 1</t>
+  </si>
+  <si>
+    <t>Out of Phase 1 automation scope.</t>
+  </si>
+  <si>
     <t>TST_MRPT_TC_2</t>
   </si>
   <si>
@@ -110,6 +122,12 @@
   </si>
   <si>
     <t>Pass</t>
+  </si>
+  <si>
+    <t>Automated</t>
+  </si>
+  <si>
+    <t>Suite: adminSchoolReports | 2026-09-16: Pass across 2 runs</t>
   </si>
   <si>
     <t>TST_MRPT_TC_3</t>
@@ -308,6 +326,12 @@
     <t>Requires the school to hold at least one "Not started" class. All six classes on VED-NEH-KVU were Active on 2026-08-26, so this needs a class whose start date is in the future.</t>
   </si>
   <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Suite: adminSchoolReports | 2026-09-16: Fail across 2 runs | Error: This case needs BOTH statuses to hold classes on this school - 'Ended' has 15 and 'Not started' has 0. With either at zero it cannot prove OR.</t>
+  </si>
+  <si>
     <t>TST_MRPT_TC_12</t>
   </si>
   <si>
@@ -434,6 +458,9 @@
   </si>
   <si>
     <t>Blocked at design time — no school available with &gt;1500 classes.</t>
+  </si>
+  <si>
+    <t>BLOCKED - see Comments for the blocker and its unblock route</t>
   </si>
   <si>
     <t>TST_MRPT_TC_18</t>
@@ -530,6 +557,9 @@
     <t>Grounded live for Class summary on 2026-08-26 — the row rendered "All items" / "All student data (up to - Aug 26, 2026)" / "496 Bytes" / Download, and generation completed within seconds despite the "we will notify you" wording. This is the fully grounded case; the other five follow the identical flow. CREATES REAL DATA: a report on the school, auto-expiring after 60 days.</t>
   </si>
   <si>
+    <t>Suite: adminSchoolReportsCreate | Not executed in this audit - status carried over, treat as unverified</t>
+  </si>
+  <si>
     <t>TST_MRPT_TC_22</t>
   </si>
   <si>
@@ -858,6 +888,12 @@
   </si>
   <si>
     <t>[ASSUMED] — the "Items" cell reads "All items" when the option is UNticked (verified live 2026-08-26); the ticked value was NOT captured. Listed in Open items. Also requires a class with an excluded component — verify one exists on VED-NEH-KVU or configure one via Class grade settings (CGST) first. CREATES REAL DATA.</t>
+  </si>
+  <si>
+    <t>Not Automated</t>
+  </si>
+  <si>
+    <t>No automated coverage.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_36</t>
@@ -1437,7 +1473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1455,7 +1491,7 @@
     <col min="14" max="14" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1498,1901 +1534,2165 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="H7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="N7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P7" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="N8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P8" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="N9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P9" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P10" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="N11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O12" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P12" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="N13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P13" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P14" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O15" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P15" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="N16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P16" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="N17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O17" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P17" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P19" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="N20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P20" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O21" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P21" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O22" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P22" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O23" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P23" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P24" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O25" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P25" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="N26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O26" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M26" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P26" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M27" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="N27" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O27" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H27" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M27" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P27" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G28" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O28" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P28" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O29" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P29" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="N32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H32" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P32" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P35" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O38" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P38" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F41" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M41" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="N41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O41" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H41" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="P41" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="O42" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O44" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>24</v>
+      <c r="P44" s="2" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="243">
   <si>
     <t>S.No.</t>
   </si>
@@ -61,10 +61,10 @@
     <t>Automation Evidence</t>
   </si>
   <si>
-    <t>TST_MRPT_TC_1</t>
-  </si>
-  <si>
-    <t>Verify the Reports tab loads with its empty state when the school has no reports</t>
+    <t>TST_MRPT_TC_2</t>
+  </si>
+  <si>
+    <t>Verify the class-selection step launches when "Create report" is clicked</t>
   </si>
   <si>
     <t>#1 — Verify Create Report is launching</t>
@@ -77,91 +77,43 @@
   </si>
   <si>
     <t>Logged in as school-admin &lt;REPORTS_ADMIN_USER&gt;; school "3 July Test School 1 (key FCN-CHZ-PDA)" opened from "My school accounts"; Reports tab open.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the school from "My school accounts".
-2. Click "REPORTS" in the school navigation.
-3. Observe the page.</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>URL is /admin/admin/org_&lt;slug&gt;/reports. The heading reads "Reports (0)". A "Create report" button is present. The informational line reads "Reports are available to download for up to 60 days". The empty state reads "No new reports available" above "Your reports will appear here after you create them", with a second "Create report" button.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. All copy captured verbatim live 2026-08-26. The (0) count is school-specific — on a school that already holds reports this case cannot show the empty state.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Not Run</t>
-  </si>
-  <si>
-    <t>Excluded - Phase 1</t>
-  </si>
-  <si>
-    <t>Out of Phase 1 automation scope.</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_2</t>
-  </si>
-  <si>
-    <t>Verify the class-selection step launches when "Create report" is clicked</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click "Create report".
 2. Observe the page.</t>
   </si>
   <si>
+    <t>—</t>
+  </si>
+  <si>
     <t>The app navigates to /admin/admin/org_&lt;slug&gt;/reports/create. The page shows a "Go back" link, the heading "Create report", the sub-heading "Choose classes you want to include in your report", a section heading "Select classes" with the note "You can include up to 1500 classes", a search box placeholdered "Search for class name or class key", a "Filter" control showing "All class statuses", a "Select all classes" checkbox, sortable column headers (Class name, Class key, Start date, End date, Students, Class status) and one selectable row per class.</t>
   </si>
   <si>
     <t>Captured live 2026-08-26. Note the "Select classes" heading carries NO count while zero classes are selected — the "(N)" appears only once at least one class is ticked.</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Pass</t>
   </si>
   <si>
     <t>Automated</t>
   </si>
   <si>
-    <t>Suite: adminSchoolReports | 2026-09-16: Pass across 2 runs</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_3</t>
-  </si>
-  <si>
-    <t>Verify the Reports tab is restored when "Go back" is used from the class-selection step</t>
-  </si>
-  <si>
-    <t>Edge</t>
-  </si>
-  <si>
-    <t>Medium</t>
+    <t>Suite: adminSchoolReports | Not executed in this audit - status carried over, treat as unverified</t>
+  </si>
+  <si>
+    <t>TST_MRPT_TC_4</t>
+  </si>
+  <si>
+    <t>Verify a class is returned when the full class name is searched</t>
+  </si>
+  <si>
+    <t>#2 — Verify search using class name or class key</t>
   </si>
   <si>
     <t>Logged in as school-admin &lt;REPORTS_ADMIN_USER&gt;; school "3 July Test School 1 (key FCN-CHZ-PDA)" opened; "Create report" clicked so the class-selection step is displayed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click the "Go back" link at the top of the class-selection step.
-2. Observe the page.</t>
-  </si>
-  <si>
-    <t>The app returns to /admin/admin/org_&lt;slug&gt;/reports, the Reports tab renders, and no new report has been created (the heading count is unchanged).</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Distinct from the footer "Cancel" (TST_MRPT_TC_18) — both exit paths need covering.</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_4</t>
-  </si>
-  <si>
-    <t>Verify a class is returned when the full class name is searched</t>
-  </si>
-  <si>
-    <t>#2 — Verify search using class name or class key</t>
   </si>
   <si>
     <t xml:space="preserve">1. Type "Fixture_GradeSettings_DO_NOT_DELETE" into the "Search for class name or class key" box.
@@ -202,6 +154,12 @@
   </si>
   <si>
     <t>Verify matching classes are returned when a partial, differently-cased term is searched</t>
+  </si>
+  <si>
+    <t>Edge</t>
+  </si>
+  <si>
+    <t>Medium</t>
   </si>
   <si>
     <t xml:space="preserve">1. Type "school license" into the search box.
@@ -326,10 +284,7 @@
     <t>Requires the school to hold at least one "Not started" class. All six classes on VED-NEH-KVU were Active on 2026-08-26, so this needs a class whose start date is in the future.</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Suite: adminSchoolReports | 2026-09-16: Fail across 2 runs | Error: This case needs BOTH statuses to hold classes on this school - 'Ended' has 15 and 'Not started' has 0. With either at zero it cannot prove OR.</t>
+    <t>Not Run</t>
   </si>
   <si>
     <t>TST_MRPT_TC_12</t>
@@ -430,37 +385,6 @@
   </si>
   <si>
     <t>Unticking the last remaining class should also remove the footer bar entirely — cross-check against TST_MRPT_TC_15.</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_17</t>
-  </si>
-  <si>
-    <t>Verify the documented 1500-class selection limit is enforced when more classes are selected</t>
-  </si>
-  <si>
-    <t>A school holding more than 1500 classes, with the class-selection step open.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select classes until the count exceeds 1500.
-2. Observe the heading, the footer bar and the "Continue" button.</t>
-  </si>
-  <si>
-    <t>&gt;1500 classes</t>
-  </si>
-  <si>
-    <t>[ASSUMED] Selection is capped at 1500 and the product surfaces the limit it states on screen ("You can include up to 1500 classes").</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. The cap text is captured verbatim live, but VED-NEH-KVU holds only 6 classes so the cap cannot be reached. UNBLOCK: a dedicated school seeded with &gt;1500 classes, or a product/API confirmation. Whether the cap blocks further ticks or raises a message is unknown.</t>
-  </si>
-  <si>
-    <t>Blocked</t>
-  </si>
-  <si>
-    <t>Blocked at design time — no school available with &gt;1500 classes.</t>
-  </si>
-  <si>
-    <t>BLOCKED - see Comments for the blocker and its unblock route</t>
   </si>
   <si>
     <t>TST_MRPT_TC_18</t>
@@ -737,46 +661,6 @@
     <t>[ASSUMED] the exact "Date range" cell format for a custom window — only the "From the beginning" form ("All student data (up to - Aug 26, 2026)") was captured live. Listed in Open items. Repeat for the other three date-capable types. CREATES REAL DATA.</t>
   </si>
   <si>
-    <t>TST_MRPT_TC_29</t>
-  </si>
-  <si>
-    <t>Verify the start date cannot be set earlier than the product floor of 1 January 2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the "Create report" dialog, choose "Class summary" and select "Custom date range".
-2. Open the "From" date picker.
-3. Navigate back past January 2022.</t>
-  </si>
-  <si>
-    <t>Boundary: 2022-01-01</t>
-  </si>
-  <si>
-    <t>Dates before 1 January 2022 are not selectable; 1 January 2022 itself is selectable.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26 from the field attributes: the "From" input carries min="2021-12-31T18:30:00.000Z", i.e. 2022-01-01 in IST. Exactly the kind of field constraint admin-shared.md §A3 requires be read before writing boundary cases.</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_30</t>
-  </si>
-  <si>
-    <t>Verify neither date can be set later than today</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the "Create report" dialog, choose "Class summary" and select "Custom date range".
-2. Open the "From" picker and attempt to select tomorrow.
-3. Repeat for the "To" picker.</t>
-  </si>
-  <si>
-    <t>Boundary: today</t>
-  </si>
-  <si>
-    <t>All dates after today are disabled in both pickers; today is selectable in both.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26: both inputs carry max="2026-08-26T18:29:59.999Z" (end of the current day). Reports cover past activity only.</t>
-  </si>
-  <si>
     <t>TST_MRPT_TC_31</t>
   </si>
   <si>
@@ -796,47 +680,6 @@
   </si>
   <si>
     <t>Verified live 2026-08-26: the "To" input carried min="2026-08-19T18:30:00.000Z" while "From" was Aug 20, 2026 — the end-date floor tracks the chosen start date. Step 4 (that the floor moves) is [ASSUMED].</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_32</t>
-  </si>
-  <si>
-    <t>Verify a date cannot be entered by typing because the date fields are read-only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the "Create report" dialog, choose "Class summary" and select "Custom date range".
-2. Click into the "From" field and type "01/01/2020".
-3. Repeat for the "To" field.</t>
-  </si>
-  <si>
-    <t>Typed input: 01/01/2020</t>
-  </si>
-  <si>
-    <t>Neither field accepts typed input; both retain their picker-set values. Dates can be set only through the calendar pickers.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26: both "From" and "To" inputs are readOnly. This rules out the whole family of "type an invalid date" negative cases — the pickers are the only input path.</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_33</t>
-  </si>
-  <si>
-    <t>Verify the custom date-range option is unavailable for report types that do not support it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tick one class and click "Continue".
-2. Choose report type "Assignments summary" and observe the "Date range" radios.
-3. Repeat for "Assignments detailed data".
-4. Repeat for "Estimated CEFR level".</t>
-  </si>
-  <si>
-    <t>Report types: Assignments summary, Assignments detailed data, Estimated CEFR level</t>
-  </si>
-  <si>
-    <t>For all three types the "Custom date range" radio remains DISABLED and "From the beginning" stays selected — no "From"/"To" fields can be produced.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26 across all seven types. Date range is supported by exactly four (Class summary, Class detailed data, Class daily data, Aggregated data), which matches the four named in scenario #12 — the scenario list is correct, and this case pins the negative half of it.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_34</t>
@@ -896,26 +739,6 @@
     <t>No automated coverage.</t>
   </si>
   <si>
-    <t>TST_MRPT_TC_36</t>
-  </si>
-  <si>
-    <t>Verify the custom grade-settings option is unavailable for the Estimated CEFR level report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tick one class and click "Continue".
-2. Choose report type "Estimated CEFR level".
-3. Observe the "Only include items that contribute to grade calculation" checkbox.</t>
-  </si>
-  <si>
-    <t>Report type: Estimated CEFR level</t>
-  </si>
-  <si>
-    <t>The checkbox is DISABLED and cannot be ticked.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26. Estimated CEFR level is the only one of the seven types supporting neither a custom date range nor custom grade settings — which is why it appears in neither scenario #12 nor #13.</t>
-  </si>
-  <si>
     <t>TST_MRPT_TC_37</t>
   </si>
   <si>
@@ -944,56 +767,6 @@
     <t>IN SCOPE — confirmed with the requester on 2026-08-26 that this seventh report type was a genuine omission from AdminApp_Report tab.xlsx, not a deliberate exclusion. It is therefore treated as a first-class report-type scenario alongside #6–#11 rather than as added coverage. Its dropdown description reads "Gives an indication of your students' level based on all tests submitted." Estimated CEFR level supports NEITHER a custom date range NOR custom grade settings (verified live 2026-08-26), so it is correctly absent from scenarios #12 and #13; those exclusions are pinned by TST_MRPT_TC_33 and TST_MRPT_TC_36. [ASSUMED] for the resulting Reports row — the report-type value and its availability were verified live, but the row was not; its shape is inherited from the grounded Class summary run. CREATES REAL DATA: a report on the school, auto-expiring after 60 days.</t>
   </si>
   <si>
-    <t>TST_MRPT_TC_38</t>
-  </si>
-  <si>
-    <t>Verify the failure dialog is shown when report generation fails</t>
-  </si>
-  <si>
-    <t>#15 — Added coverage: report generation error paths</t>
-  </si>
-  <si>
-    <t>The class-selection step is open and the report-generation backend is forced to fail.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tick one class and click "Continue".
-2. Choose any report type.
-3. Click "Submit" while report generation is failing.
-4. Observe the dialog.</t>
-  </si>
-  <si>
-    <t>A dialog is shown headed "Sorry, something went wrong. The report you requested was not generated." offering "Try again" and "Back to Reports".</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. The copy above was captured verbatim from the PRE-RENDERED DOM on 2026-08-26 (admin-shared.md §A6 free-capture), so the expected result is verified even though the state was never reached. UNBLOCK: backend fault injection or a stubbed failure response. A second, separate failure surface exists on the Reports tab itself — see TST_MRPT_TC_39.</t>
-  </si>
-  <si>
-    <t>Blocked at design time — report generation failure cannot be forced on Thor.</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_39</t>
-  </si>
-  <si>
-    <t>Verify the partial-failure detail modal lists the excluded classes when a report is created with errors</t>
-  </si>
-  <si>
-    <t>The Reports tab holds a report that was generated with per-class errors.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the Reports tab.
-2. Open the error detail for a report created with errors.
-3. Observe the modal.</t>
-  </si>
-  <si>
-    <t>A modal headed "Report created with errors" states "&lt;N&gt; out of &lt;TOTAL&gt; classes were not included in your report due to the errors shown below" above a table with the columns "Class name", "Class key" and "Error message", and offers "Download report".</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. Copy captured from the pre-rendered DOM on the Reports tab 2026-08-26. Requires a multi-class report in which some classes fail — cannot be produced on demand. UNBLOCK: fault injection, or a class deliberately placed in a state that fails report generation.</t>
-  </si>
-  <si>
-    <t>Blocked at design time — a partially-failing report cannot be produced on Thor.</t>
-  </si>
-  <si>
     <t>TST_MRPT_TC_40</t>
   </si>
   <si>
@@ -1060,7 +833,13 @@
     <t>Added 2026-09-01 from the other team's TC_REP_014, which sweeps the exclusion across all six types. Our TST_MRPT_TC_35 proves the option takes effect on ONE report; consistency across types was untested — and inconsistency between report types is precisely the defect this guards against. Depends on the same fixture as TST_MRPT_TC_41.</t>
   </si>
   <si>
+    <t>Blocked</t>
+  </si>
+  <si>
     <t>Blocked at design time. The frozen-activity fixture it needed NOW EXISTS (Automation_frozen_DND / gHoZ-iBXf, provisioned 2026-09-11 and used by TST_MRPT_TC_41), so the remaining blocker is narrower than it was: that class still needs ONE COMPONENT EXCLUDED from its grade settings, and activity on the excluded item. Once that is configured this case can follow TST_MRPT_TC_41 directly.</t>
+  </si>
+  <si>
+    <t>BLOCKED - see Comments for the blocker and its unblock route</t>
   </si>
   <si>
     <t>TST_MRPT_TC_43</t>
@@ -1473,7 +1252,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1543,7 +1322,7 @@
     </row>
     <row r="2" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>16</v>
@@ -1593,7 +1372,7 @@
     </row>
     <row r="3" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>30</v>
@@ -1602,7 +1381,7 @@
         <v>31</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>19</v>
@@ -1611,39 +1390,39 @@
         <v>20</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>38</v>
@@ -1652,28 +1431,28 @@
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>26</v>
@@ -1693,75 +1472,75 @@
     </row>
     <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="L5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>55</v>
@@ -1779,21 +1558,21 @@
         <v>26</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>59</v>
@@ -1802,22 +1581,22 @@
         <v>60</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>63</v>
@@ -1829,21 +1608,21 @@
         <v>26</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>65</v>
@@ -1852,116 +1631,116 @@
         <v>66</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="L8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="L9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>80</v>
@@ -1979,430 +1758,430 @@
         <v>26</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="I13" s="2" t="s">
+      <c r="J13" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="L13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="I14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="L14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="I15" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="L15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="L16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="K17" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="L17" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="J18" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="L18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>136</v>
+        <v>27</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>137</v>
+        <v>26</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>136</v>
+        <v>28</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>19</v>
@@ -2411,148 +2190,148 @@
         <v>20</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I20" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="L20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="G21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="J21" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>19</v>
@@ -2561,148 +2340,148 @@
         <v>20</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>19</v>
@@ -2711,148 +2490,148 @@
         <v>20</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>165</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="K27" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>172</v>
-      </c>
       <c r="L27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>165</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>19</v>
@@ -2861,48 +2640,48 @@
         <v>20</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>19</v>
@@ -2911,70 +2690,70 @@
         <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>42</v>
+        <v>201</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O29" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="P29" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="E30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="K30" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="L30" s="2" t="s">
         <v>26</v>
       </c>
@@ -2988,42 +2767,42 @@
         <v>28</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>29</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J31" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="K31" s="2" t="s">
         <v>219</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>26</v>
@@ -3043,75 +2822,75 @@
     </row>
     <row r="32" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H32" s="2" t="s">
+      <c r="I32" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="J32" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="J32" s="2" t="s">
+      <c r="K32" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="L32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>37</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>230</v>
@@ -3129,51 +2908,51 @@
         <v>26</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>27</v>
+        <v>234</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>26</v>
+        <v>235</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>28</v>
+        <v>234</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>29</v>
+        <v>236</v>
       </c>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>199</v>
+        <v>136</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>26</v>
@@ -3188,507 +2967,7 @@
         <v>28</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P41" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="P43" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P44" s="2" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="245">
   <si>
     <t>S.No.</t>
   </si>
@@ -101,7 +101,7 @@
     <t>Automated</t>
   </si>
   <si>
-    <t>Suite: adminSchoolReports | Not executed in this audit - status carried over, treat as unverified</t>
+    <t>Suite: adminSchoolReports | 2026-09-16: Pass across 2 runs</t>
   </si>
   <si>
     <t>TST_MRPT_TC_4</t>
@@ -284,7 +284,10 @@
     <t>Requires the school to hold at least one "Not started" class. All six classes on VED-NEH-KVU were Active on 2026-08-26, so this needs a class whose start date is in the future.</t>
   </si>
   <si>
-    <t>Not Run</t>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Suite: adminSchoolReports | 2026-09-16: Fail across 2 runs | Error: This case needs BOTH statuses to hold classes on this school - 'Ended' has 15 and 'Not started' has 0. With either at zero it cannot prove OR.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_12</t>
@@ -731,6 +734,9 @@
   </si>
   <si>
     <t>[ASSUMED] — the "Items" cell reads "All items" when the option is UNticked (verified live 2026-08-26); the ticked value was NOT captured. Listed in Open items. Also requires a class with an excluded component — verify one exists on VED-NEH-KVU or configure one via Class grade settings (CGST) first. CREATES REAL DATA.</t>
+  </si>
+  <si>
+    <t>Not Run</t>
   </si>
   <si>
     <t>Not Automated</t>
@@ -1767,7 +1773,7 @@
         <v>28</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1775,10 +1781,10 @@
         <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>61</v>
@@ -1793,16 +1799,16 @@
         <v>33</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>26</v>
@@ -1825,13 +1831,13 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>19</v>
@@ -1843,16 +1849,16 @@
         <v>33</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>26</v>
@@ -1875,13 +1881,13 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>19</v>
@@ -1893,16 +1899,16 @@
         <v>33</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>26</v>
@@ -1925,13 +1931,13 @@
         <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>46</v>
@@ -1943,16 +1949,16 @@
         <v>33</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>26</v>
@@ -1975,13 +1981,13 @@
         <v>16</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>46</v>
@@ -1993,16 +1999,16 @@
         <v>33</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>26</v>
@@ -2025,13 +2031,13 @@
         <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>19</v>
@@ -2043,16 +2049,16 @@
         <v>33</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>26</v>
@@ -2075,13 +2081,13 @@
         <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>19</v>
@@ -2093,16 +2099,16 @@
         <v>33</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>26</v>
@@ -2125,13 +2131,13 @@
         <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>46</v>
@@ -2143,16 +2149,16 @@
         <v>33</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>26</v>
@@ -2175,13 +2181,13 @@
         <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>19</v>
@@ -2193,16 +2199,16 @@
         <v>33</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>26</v>
@@ -2217,7 +2223,7 @@
         <v>28</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2225,13 +2231,13 @@
         <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>19</v>
@@ -2243,16 +2249,16 @@
         <v>33</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>26</v>
@@ -2267,7 +2273,7 @@
         <v>28</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2275,13 +2281,13 @@
         <v>23</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>19</v>
@@ -2293,16 +2299,16 @@
         <v>33</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>26</v>
@@ -2317,7 +2323,7 @@
         <v>28</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2325,13 +2331,13 @@
         <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>19</v>
@@ -2343,16 +2349,16 @@
         <v>33</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>26</v>
@@ -2367,7 +2373,7 @@
         <v>28</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2375,13 +2381,13 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>19</v>
@@ -2393,16 +2399,16 @@
         <v>33</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>26</v>
@@ -2417,7 +2423,7 @@
         <v>28</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2425,13 +2431,13 @@
         <v>26</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>19</v>
@@ -2443,16 +2449,16 @@
         <v>33</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>26</v>
@@ -2467,7 +2473,7 @@
         <v>28</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2475,13 +2481,13 @@
         <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>19</v>
@@ -2493,16 +2499,16 @@
         <v>33</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>26</v>
@@ -2525,13 +2531,13 @@
         <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>19</v>
@@ -2543,16 +2549,16 @@
         <v>33</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>26</v>
@@ -2567,7 +2573,7 @@
         <v>28</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2575,13 +2581,13 @@
         <v>31</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>46</v>
@@ -2593,16 +2599,16 @@
         <v>33</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>26</v>
@@ -2625,13 +2631,13 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>19</v>
@@ -2643,16 +2649,16 @@
         <v>33</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>26</v>
@@ -2675,13 +2681,13 @@
         <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>19</v>
@@ -2690,34 +2696,34 @@
         <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>84</v>
+        <v>207</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2725,13 +2731,13 @@
         <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>19</v>
@@ -2743,16 +2749,16 @@
         <v>33</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>26</v>
@@ -2767,7 +2773,7 @@
         <v>28</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2775,10 +2781,10 @@
         <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>61</v>
@@ -2793,16 +2799,16 @@
         <v>33</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>26</v>
@@ -2825,13 +2831,13 @@
         <v>41</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>19</v>
@@ -2840,19 +2846,19 @@
         <v>20</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>26</v>
@@ -2867,7 +2873,7 @@
         <v>28</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2875,13 +2881,13 @@
         <v>42</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>46</v>
@@ -2890,34 +2896,34 @@
         <v>47</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2925,13 +2931,13 @@
         <v>43</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>19</v>
@@ -2943,16 +2949,16 @@
         <v>33</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>26</v>
@@ -2967,7 +2973,7 @@
         <v>28</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
+++ b/testAutomation_v1.0/test/Manual/C1App/AdminApp-Reports/AdminApp_Reports_tab_test_cases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="245">
   <si>
     <t>S.No.</t>
   </si>
@@ -61,10 +61,10 @@
     <t>Automation Evidence</t>
   </si>
   <si>
-    <t>TST_MRPT_TC_1</t>
-  </si>
-  <si>
-    <t>Verify the Reports tab loads with its empty state when the school has no reports</t>
+    <t>TST_MRPT_TC_2</t>
+  </si>
+  <si>
+    <t>Verify the class-selection step launches when "Create report" is clicked</t>
   </si>
   <si>
     <t>#1 — Verify Create Report is launching</t>
@@ -77,50 +77,24 @@
   </si>
   <si>
     <t>Logged in as school-admin &lt;REPORTS_ADMIN_USER&gt;; school "3 July Test School 1 (key FCN-CHZ-PDA)" opened from "My school accounts"; Reports tab open.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the school from "My school accounts".
-2. Click "REPORTS" in the school navigation.
-3. Observe the page.</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>URL is /admin/admin/org_&lt;slug&gt;/reports. The heading reads "Reports (0)". A "Create report" button is present. The informational line reads "Reports are available to download for up to 60 days". The empty state reads "No new reports available" above "Your reports will appear here after you create them", with a second "Create report" button.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. All copy captured verbatim live 2026-08-26. The (0) count is school-specific — on a school that already holds reports this case cannot show the empty state.</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Not Run</t>
-  </si>
-  <si>
-    <t>Excluded - Phase 1</t>
-  </si>
-  <si>
-    <t>Out of Phase 1 automation scope.</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_2</t>
-  </si>
-  <si>
-    <t>Verify the class-selection step launches when "Create report" is clicked</t>
   </si>
   <si>
     <t xml:space="preserve">1. Click "Create report".
 2. Observe the page.</t>
   </si>
   <si>
+    <t>—</t>
+  </si>
+  <si>
     <t>The app navigates to /admin/admin/org_&lt;slug&gt;/reports/create. The page shows a "Go back" link, the heading "Create report", the sub-heading "Choose classes you want to include in your report", a section heading "Select classes" with the note "You can include up to 1500 classes", a search box placeholdered "Search for class name or class key", a "Filter" control showing "All class statuses", a "Select all classes" checkbox, sortable column headers (Class name, Class key, Start date, End date, Students, Class status) and one selectable row per class.</t>
   </si>
   <si>
     <t>Captured live 2026-08-26. Note the "Select classes" heading carries NO count while zero classes are selected — the "(N)" appears only once at least one class is ticked.</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>Pass</t>
   </si>
   <si>
@@ -130,38 +104,16 @@
     <t>Suite: adminSchoolReports | 2026-09-16: Pass across 2 runs</t>
   </si>
   <si>
-    <t>TST_MRPT_TC_3</t>
-  </si>
-  <si>
-    <t>Verify the Reports tab is restored when "Go back" is used from the class-selection step</t>
-  </si>
-  <si>
-    <t>Edge</t>
-  </si>
-  <si>
-    <t>Medium</t>
+    <t>TST_MRPT_TC_4</t>
+  </si>
+  <si>
+    <t>Verify a class is returned when the full class name is searched</t>
+  </si>
+  <si>
+    <t>#2 — Verify search using class name or class key</t>
   </si>
   <si>
     <t>Logged in as school-admin &lt;REPORTS_ADMIN_USER&gt;; school "3 July Test School 1 (key FCN-CHZ-PDA)" opened; "Create report" clicked so the class-selection step is displayed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click the "Go back" link at the top of the class-selection step.
-2. Observe the page.</t>
-  </si>
-  <si>
-    <t>The app returns to /admin/admin/org_&lt;slug&gt;/reports, the Reports tab renders, and no new report has been created (the heading count is unchanged).</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Distinct from the footer "Cancel" (TST_MRPT_TC_18) — both exit paths need covering.</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_4</t>
-  </si>
-  <si>
-    <t>Verify a class is returned when the full class name is searched</t>
-  </si>
-  <si>
-    <t>#2 — Verify search using class name or class key</t>
   </si>
   <si>
     <t xml:space="preserve">1. Type "Fixture_GradeSettings_DO_NOT_DELETE" into the "Search for class name or class key" box.
@@ -202,6 +154,12 @@
   </si>
   <si>
     <t>Verify matching classes are returned when a partial, differently-cased term is searched</t>
+  </si>
+  <si>
+    <t>Edge</t>
+  </si>
+  <si>
+    <t>Medium</t>
   </si>
   <si>
     <t xml:space="preserve">1. Type "school license" into the search box.
@@ -430,37 +388,6 @@
   </si>
   <si>
     <t>Unticking the last remaining class should also remove the footer bar entirely — cross-check against TST_MRPT_TC_15.</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_17</t>
-  </si>
-  <si>
-    <t>Verify the documented 1500-class selection limit is enforced when more classes are selected</t>
-  </si>
-  <si>
-    <t>A school holding more than 1500 classes, with the class-selection step open.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select classes until the count exceeds 1500.
-2. Observe the heading, the footer bar and the "Continue" button.</t>
-  </si>
-  <si>
-    <t>&gt;1500 classes</t>
-  </si>
-  <si>
-    <t>[ASSUMED] Selection is capped at 1500 and the product surfaces the limit it states on screen ("You can include up to 1500 classes").</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. The cap text is captured verbatim live, but VED-NEH-KVU holds only 6 classes so the cap cannot be reached. UNBLOCK: a dedicated school seeded with &gt;1500 classes, or a product/API confirmation. Whether the cap blocks further ticks or raises a message is unknown.</t>
-  </si>
-  <si>
-    <t>Blocked</t>
-  </si>
-  <si>
-    <t>Blocked at design time — no school available with &gt;1500 classes.</t>
-  </si>
-  <si>
-    <t>BLOCKED - see Comments for the blocker and its unblock route</t>
   </si>
   <si>
     <t>TST_MRPT_TC_18</t>
@@ -737,46 +664,6 @@
     <t>[ASSUMED] the exact "Date range" cell format for a custom window — only the "From the beginning" form ("All student data (up to - Aug 26, 2026)") was captured live. Listed in Open items. Repeat for the other three date-capable types. CREATES REAL DATA.</t>
   </si>
   <si>
-    <t>TST_MRPT_TC_29</t>
-  </si>
-  <si>
-    <t>Verify the start date cannot be set earlier than the product floor of 1 January 2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the "Create report" dialog, choose "Class summary" and select "Custom date range".
-2. Open the "From" date picker.
-3. Navigate back past January 2022.</t>
-  </si>
-  <si>
-    <t>Boundary: 2022-01-01</t>
-  </si>
-  <si>
-    <t>Dates before 1 January 2022 are not selectable; 1 January 2022 itself is selectable.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26 from the field attributes: the "From" input carries min="2021-12-31T18:30:00.000Z", i.e. 2022-01-01 in IST. Exactly the kind of field constraint admin-shared.md §A3 requires be read before writing boundary cases.</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_30</t>
-  </si>
-  <si>
-    <t>Verify neither date can be set later than today</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the "Create report" dialog, choose "Class summary" and select "Custom date range".
-2. Open the "From" picker and attempt to select tomorrow.
-3. Repeat for the "To" picker.</t>
-  </si>
-  <si>
-    <t>Boundary: today</t>
-  </si>
-  <si>
-    <t>All dates after today are disabled in both pickers; today is selectable in both.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26: both inputs carry max="2026-08-26T18:29:59.999Z" (end of the current day). Reports cover past activity only.</t>
-  </si>
-  <si>
     <t>TST_MRPT_TC_31</t>
   </si>
   <si>
@@ -796,47 +683,6 @@
   </si>
   <si>
     <t>Verified live 2026-08-26: the "To" input carried min="2026-08-19T18:30:00.000Z" while "From" was Aug 20, 2026 — the end-date floor tracks the chosen start date. Step 4 (that the floor moves) is [ASSUMED].</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_32</t>
-  </si>
-  <si>
-    <t>Verify a date cannot be entered by typing because the date fields are read-only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the "Create report" dialog, choose "Class summary" and select "Custom date range".
-2. Click into the "From" field and type "01/01/2020".
-3. Repeat for the "To" field.</t>
-  </si>
-  <si>
-    <t>Typed input: 01/01/2020</t>
-  </si>
-  <si>
-    <t>Neither field accepts typed input; both retain their picker-set values. Dates can be set only through the calendar pickers.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26: both "From" and "To" inputs are readOnly. This rules out the whole family of "type an invalid date" negative cases — the pickers are the only input path.</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_33</t>
-  </si>
-  <si>
-    <t>Verify the custom date-range option is unavailable for report types that do not support it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tick one class and click "Continue".
-2. Choose report type "Assignments summary" and observe the "Date range" radios.
-3. Repeat for "Assignments detailed data".
-4. Repeat for "Estimated CEFR level".</t>
-  </si>
-  <si>
-    <t>Report types: Assignments summary, Assignments detailed data, Estimated CEFR level</t>
-  </si>
-  <si>
-    <t>For all three types the "Custom date range" radio remains DISABLED and "From the beginning" stays selected — no "From"/"To" fields can be produced.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26 across all seven types. Date range is supported by exactly four (Class summary, Class detailed data, Class daily data, Aggregated data), which matches the four named in scenario #12 — the scenario list is correct, and this case pins the negative half of it.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_34</t>
@@ -890,30 +736,13 @@
     <t>[ASSUMED] — the "Items" cell reads "All items" when the option is UNticked (verified live 2026-08-26); the ticked value was NOT captured. Listed in Open items. Also requires a class with an excluded component — verify one exists on VED-NEH-KVU or configure one via Class grade settings (CGST) first. CREATES REAL DATA.</t>
   </si>
   <si>
+    <t>Not Run</t>
+  </si>
+  <si>
     <t>Not Automated</t>
   </si>
   <si>
     <t>No automated coverage.</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_36</t>
-  </si>
-  <si>
-    <t>Verify the custom grade-settings option is unavailable for the Estimated CEFR level report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tick one class and click "Continue".
-2. Choose report type "Estimated CEFR level".
-3. Observe the "Only include items that contribute to grade calculation" checkbox.</t>
-  </si>
-  <si>
-    <t>Report type: Estimated CEFR level</t>
-  </si>
-  <si>
-    <t>The checkbox is DISABLED and cannot be ticked.</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. Verified live 2026-08-26. Estimated CEFR level is the only one of the seven types supporting neither a custom date range nor custom grade settings — which is why it appears in neither scenario #12 nor #13.</t>
   </si>
   <si>
     <t>TST_MRPT_TC_37</t>
@@ -944,56 +773,6 @@
     <t>IN SCOPE — confirmed with the requester on 2026-08-26 that this seventh report type was a genuine omission from AdminApp_Report tab.xlsx, not a deliberate exclusion. It is therefore treated as a first-class report-type scenario alongside #6–#11 rather than as added coverage. Its dropdown description reads "Gives an indication of your students' level based on all tests submitted." Estimated CEFR level supports NEITHER a custom date range NOR custom grade settings (verified live 2026-08-26), so it is correctly absent from scenarios #12 and #13; those exclusions are pinned by TST_MRPT_TC_33 and TST_MRPT_TC_36. [ASSUMED] for the resulting Reports row — the report-type value and its availability were verified live, but the row was not; its shape is inherited from the grounded Class summary run. CREATES REAL DATA: a report on the school, auto-expiring after 60 days.</t>
   </si>
   <si>
-    <t>TST_MRPT_TC_38</t>
-  </si>
-  <si>
-    <t>Verify the failure dialog is shown when report generation fails</t>
-  </si>
-  <si>
-    <t>#15 — Added coverage: report generation error paths</t>
-  </si>
-  <si>
-    <t>The class-selection step is open and the report-generation backend is forced to fail.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Tick one class and click "Continue".
-2. Choose any report type.
-3. Click "Submit" while report generation is failing.
-4. Observe the dialog.</t>
-  </si>
-  <si>
-    <t>A dialog is shown headed "Sorry, something went wrong. The report you requested was not generated." offering "Try again" and "Back to Reports".</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. The copy above was captured verbatim from the PRE-RENDERED DOM on 2026-08-26 (admin-shared.md §A6 free-capture), so the expected result is verified even though the state was never reached. UNBLOCK: backend fault injection or a stubbed failure response. A second, separate failure surface exists on the Reports tab itself — see TST_MRPT_TC_39.</t>
-  </si>
-  <si>
-    <t>Blocked at design time — report generation failure cannot be forced on Thor.</t>
-  </si>
-  <si>
-    <t>TST_MRPT_TC_39</t>
-  </si>
-  <si>
-    <t>Verify the partial-failure detail modal lists the excluded classes when a report is created with errors</t>
-  </si>
-  <si>
-    <t>The Reports tab holds a report that was generated with per-class errors.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Open the Reports tab.
-2. Open the error detail for a report created with errors.
-3. Observe the modal.</t>
-  </si>
-  <si>
-    <t>A modal headed "Report created with errors" states "&lt;N&gt; out of &lt;TOTAL&gt; classes were not included in your report due to the errors shown below" above a table with the columns "Class name", "Class key" and "Error message", and offers "Download report".</t>
-  </si>
-  <si>
-    <t>**[EXTRA — Phase 1 exclusion]** Not present in the other team's reviewed sheet (`Admin_Gap_Analysis.xlsx`, status "Extra in Ours"). **This case will NOT be automated in Phase 1** — exclude it from the Phase 1 automation scope; revisit for a later phase. BLOCKED at design time. Copy captured from the pre-rendered DOM on the Reports tab 2026-08-26. Requires a multi-class report in which some classes fail — cannot be produced on demand. UNBLOCK: fault injection, or a class deliberately placed in a state that fails report generation.</t>
-  </si>
-  <si>
-    <t>Blocked at design time — a partially-failing report cannot be produced on Thor.</t>
-  </si>
-  <si>
     <t>TST_MRPT_TC_40</t>
   </si>
   <si>
@@ -1060,7 +839,13 @@
     <t>Added 2026-09-01 from the other team's TC_REP_014, which sweeps the exclusion across all six types. Our TST_MRPT_TC_35 proves the option takes effect on ONE report; consistency across types was untested — and inconsistency between report types is precisely the defect this guards against. Depends on the same fixture as TST_MRPT_TC_41.</t>
   </si>
   <si>
+    <t>Blocked</t>
+  </si>
+  <si>
     <t>Blocked at design time. The frozen-activity fixture it needed NOW EXISTS (Automation_frozen_DND / gHoZ-iBXf, provisioned 2026-09-11 and used by TST_MRPT_TC_41), so the remaining blocker is narrower than it was: that class still needs ONE COMPONENT EXCLUDED from its grade settings, and activity on the excluded item. Once that is configured this case can follow TST_MRPT_TC_41 directly.</t>
+  </si>
+  <si>
+    <t>BLOCKED - see Comments for the blocker and its unblock route</t>
   </si>
   <si>
     <t>TST_MRPT_TC_43</t>
@@ -1473,7 +1258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
@@ -1543,7 +1328,7 @@
     </row>
     <row r="2" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>16</v>
@@ -1593,7 +1378,7 @@
     </row>
     <row r="3" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>30</v>
@@ -1602,7 +1387,7 @@
         <v>31</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>19</v>
@@ -1611,39 +1396,39 @@
         <v>20</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>38</v>
@@ -1652,28 +1437,28 @@
         <v>39</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>26</v>
@@ -1693,75 +1478,75 @@
     </row>
     <row r="5" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="L5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="F6" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>55</v>
@@ -1779,21 +1564,21 @@
         <v>26</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>59</v>
@@ -1802,22 +1587,22 @@
         <v>60</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>63</v>
@@ -1829,21 +1614,21 @@
         <v>26</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>65</v>
@@ -1852,116 +1637,116 @@
         <v>66</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="L8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="L9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>20</v>
-      </c>
       <c r="G10" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>80</v>
@@ -1979,121 +1764,121 @@
         <v>26</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>37</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>99</v>
@@ -2102,16 +1887,16 @@
         <v>100</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>101</v>
@@ -2129,21 +1914,21 @@
         <v>26</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>105</v>
@@ -2152,122 +1937,122 @@
         <v>106</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="L14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="L15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="E16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>121</v>
@@ -2279,21 +2064,21 @@
         <v>26</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>123</v>
@@ -2302,16 +2087,16 @@
         <v>124</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>125</v>
@@ -2329,21 +2114,21 @@
         <v>26</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>129</v>
@@ -2352,57 +2137,57 @@
         <v>130</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="I18" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="L18" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>136</v>
+        <v>27</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>137</v>
+        <v>26</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>136</v>
+        <v>28</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>19</v>
@@ -2411,148 +2196,148 @@
         <v>20</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H19" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P19" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J20" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="I20" s="2" t="s">
+      <c r="K20" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="J20" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="L20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
+        <v>23</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="G21" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H21" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="J21" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="K21" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>19</v>
@@ -2561,148 +2346,148 @@
         <v>20</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="I22" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="K22" s="2" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>19</v>
@@ -2711,148 +2496,148 @@
         <v>20</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>165</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="K27" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>172</v>
-      </c>
       <c r="L27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>165</v>
+        <v>29</v>
       </c>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>19</v>
@@ -2861,48 +2646,48 @@
         <v>20</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>19</v>
@@ -2911,39 +2696,39 @@
         <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>42</v>
+        <v>202</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="L29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="N29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="O29" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="K29" s="2" t="s">
+      <c r="P29" s="2" t="s">
         <v>209</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>210</v>
@@ -2952,28 +2737,28 @@
         <v>211</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>26</v>
@@ -2988,36 +2773,36 @@
         <v>28</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>29</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>199</v>
+        <v>61</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>219</v>
+        <v>23</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>220</v>
@@ -3043,7 +2828,7 @@
     </row>
     <row r="32" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>222</v>
@@ -3052,128 +2837,128 @@
         <v>223</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>42</v>
+        <v>224</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>26</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>37</v>
+        <v>142</v>
       </c>
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>42</v>
+        <v>231</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>27</v>
+        <v>236</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>26</v>
+        <v>237</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>28</v>
+        <v>236</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>29</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>20</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>26</v>
@@ -3188,507 +2973,7 @@
         <v>28</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2">
-        <v>34</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2">
-        <v>35</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="K37" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M38" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2">
-        <v>38</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
-        <v>39</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="P40" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2">
-        <v>40</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F41" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P41" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
-        <v>41</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2">
-        <v>42</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="P43" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2">
-        <v>43</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="P44" s="2" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
